--- a/_project/SEO-CONTENT-CLUSTER-PLAN-2026-09-14.xlsx
+++ b/_project/SEO-CONTENT-CLUSTER-PLAN-2026-09-14.xlsx
@@ -9,17 +9,19 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Read me" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Current URL inventory" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword allocation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clusters and gaps" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposed URLs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal linking queue" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Editorial readiness" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Keyword allocation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Clusters and gaps" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Proposed URLs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Internal linking queue" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current URL inventory'!$A$1:$K$178</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Keyword allocation'!$A$1:$V$718</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Clusters and gaps'!$A$1:$G$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Proposed URLs'!$A$1:$I$60</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Internal linking queue'!$A$1:$E$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Current URL inventory'!$A$1:$M$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Editorial readiness'!$A$1:$L$119</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Keyword allocation'!$A$1:$V$718</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Clusters and gaps'!$A$1:$G$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Proposed URLs'!$A$1:$I$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Internal linking queue'!$A$1:$E$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -544,7 +546,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K178"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -557,7 +559,9 @@
     <col width="58" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -613,6 +617,16 @@
       </c>
       <c r="K1" s="3" t="inlineStr">
         <is>
+          <t>Source count</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Long-form readiness</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
           <t>Internal-link role</t>
         </is>
       </c>
@@ -664,7 +678,15 @@
       <c r="J2" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1039 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -717,7 +739,15 @@
       <c r="J3" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1024 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -770,7 +800,15 @@
       <c r="J4" s="2" t="n">
         <v>83</v>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1117 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -823,7 +861,15 @@
       <c r="J5" s="2" t="n">
         <v>516</v>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Needs 684 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -876,7 +922,15 @@
       <c r="J6" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="K6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1105 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -929,7 +983,15 @@
       <c r="J7" s="2" t="n">
         <v>1426</v>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -982,7 +1044,15 @@
       <c r="J8" s="2" t="n">
         <v>228</v>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Needs 972 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1035,7 +1105,15 @@
       <c r="J9" s="2" t="n">
         <v>383</v>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Needs 817 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1088,7 +1166,15 @@
       <c r="J10" s="2" t="n">
         <v>580</v>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Needs 620 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1141,7 +1227,15 @@
       <c r="J11" s="2" t="n">
         <v>1440</v>
       </c>
-      <c r="K11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1194,7 +1288,15 @@
       <c r="J12" s="2" t="n">
         <v>1424</v>
       </c>
-      <c r="K12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1247,7 +1349,15 @@
       <c r="J13" s="2" t="n">
         <v>1416</v>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1300,7 +1410,15 @@
       <c r="J14" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="K14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1023 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1353,7 +1471,15 @@
       <c r="J15" s="2" t="n">
         <v>186</v>
       </c>
-      <c r="K15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1014 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1406,7 +1532,15 @@
       <c r="J16" s="2" t="n">
         <v>1439</v>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1459,7 +1593,15 @@
       <c r="J17" s="2" t="n">
         <v>1439</v>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1512,7 +1654,15 @@
       <c r="J18" s="2" t="n">
         <v>600</v>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Needs 600 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1565,7 +1715,15 @@
       <c r="J19" s="2" t="n">
         <v>473</v>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Needs 727 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1618,7 +1776,15 @@
       <c r="J20" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1024 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1671,7 +1837,15 @@
       <c r="J21" s="2" t="n">
         <v>126</v>
       </c>
-      <c r="K21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1724,7 +1898,15 @@
       <c r="J22" s="2" t="n">
         <v>145</v>
       </c>
-      <c r="K22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1777,7 +1959,15 @@
       <c r="J23" s="2" t="n">
         <v>785</v>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Needs 415 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1830,7 +2020,15 @@
       <c r="J24" s="2" t="n">
         <v>96</v>
       </c>
-      <c r="K24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1104 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1883,7 +2081,15 @@
       <c r="J25" s="2" t="n">
         <v>788</v>
       </c>
-      <c r="K25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Needs 412 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1936,7 +2142,15 @@
       <c r="J26" s="2" t="n">
         <v>214</v>
       </c>
-      <c r="K26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Needs 986 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -1989,7 +2203,15 @@
       <c r="J27" s="2" t="n">
         <v>607</v>
       </c>
-      <c r="K27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Needs 593 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2042,7 +2264,15 @@
       <c r="J28" s="2" t="n">
         <v>799</v>
       </c>
-      <c r="K28" s="2" t="inlineStr">
+      <c r="K28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Needs 401 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2095,7 +2325,15 @@
       <c r="J29" s="2" t="n">
         <v>381</v>
       </c>
-      <c r="K29" s="2" t="inlineStr">
+      <c r="K29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Needs 819 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2148,7 +2386,15 @@
       <c r="J30" s="2" t="n">
         <v>794</v>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="K30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Needs 406 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2201,7 +2447,15 @@
       <c r="J31" s="2" t="n">
         <v>755</v>
       </c>
-      <c r="K31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Needs 445 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2254,7 +2508,15 @@
       <c r="J32" s="2" t="n">
         <v>147</v>
       </c>
-      <c r="K32" s="2" t="inlineStr">
+      <c r="K32" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2307,7 +2569,15 @@
       <c r="J33" s="2" t="n">
         <v>212</v>
       </c>
-      <c r="K33" s="2" t="inlineStr">
+      <c r="K33" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2360,7 +2630,15 @@
       <c r="J34" s="2" t="n">
         <v>139</v>
       </c>
-      <c r="K34" s="2" t="inlineStr">
+      <c r="K34" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2413,7 +2691,15 @@
       <c r="J35" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="K35" s="2" t="inlineStr">
+      <c r="K35" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2466,7 +2752,15 @@
       <c r="J36" s="2" t="n">
         <v>204</v>
       </c>
-      <c r="K36" s="2" t="inlineStr">
+      <c r="K36" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2519,7 +2813,15 @@
       <c r="J37" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K37" s="2" t="inlineStr">
+      <c r="K37" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2572,7 +2874,15 @@
       <c r="J38" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="K38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2625,7 +2935,15 @@
       <c r="J39" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K39" s="2" t="inlineStr">
+      <c r="K39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2678,7 +2996,15 @@
       <c r="J40" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="K40" s="2" t="inlineStr">
+      <c r="K40" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2731,7 +3057,15 @@
       <c r="J41" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="K41" s="2" t="inlineStr">
+      <c r="K41" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2784,7 +3118,15 @@
       <c r="J42" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="K42" s="2" t="inlineStr">
+      <c r="K42" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2837,7 +3179,15 @@
       <c r="J43" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="K43" s="2" t="inlineStr">
+      <c r="K43" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2890,7 +3240,15 @@
       <c r="J44" s="2" t="n">
         <v>158</v>
       </c>
-      <c r="K44" s="2" t="inlineStr">
+      <c r="K44" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2943,7 +3301,15 @@
       <c r="J45" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="K45" s="2" t="inlineStr">
+      <c r="K45" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -2996,7 +3362,15 @@
       <c r="J46" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="K46" s="2" t="inlineStr">
+      <c r="K46" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3049,7 +3423,15 @@
       <c r="J47" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K47" s="2" t="inlineStr">
+      <c r="K47" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3102,7 +3484,15 @@
       <c r="J48" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="K48" s="2" t="inlineStr">
+      <c r="K48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Needs 991 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3155,7 +3545,15 @@
       <c r="J49" s="2" t="n">
         <v>1433</v>
       </c>
-      <c r="K49" s="2" t="inlineStr">
+      <c r="K49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3208,7 +3606,15 @@
       <c r="J50" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="K50" s="2" t="inlineStr">
+      <c r="K50" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3261,7 +3667,15 @@
       <c r="J51" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="K51" s="2" t="inlineStr">
+      <c r="K51" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3314,7 +3728,15 @@
       <c r="J52" s="2" t="n">
         <v>176</v>
       </c>
-      <c r="K52" s="2" t="inlineStr">
+      <c r="K52" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3367,7 +3789,15 @@
       <c r="J53" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="K53" s="2" t="inlineStr">
+      <c r="K53" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3420,7 +3850,15 @@
       <c r="J54" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="K54" s="2" t="inlineStr">
+      <c r="K54" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3473,7 +3911,15 @@
       <c r="J55" s="2" t="n">
         <v>188</v>
       </c>
-      <c r="K55" s="2" t="inlineStr">
+      <c r="K55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1012 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3526,7 +3972,15 @@
       <c r="J56" s="2" t="n">
         <v>154</v>
       </c>
-      <c r="K56" s="2" t="inlineStr">
+      <c r="K56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1046 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3579,7 +4033,15 @@
       <c r="J57" s="2" t="n">
         <v>94</v>
       </c>
-      <c r="K57" s="2" t="inlineStr">
+      <c r="K57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1106 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3632,7 +4094,15 @@
       <c r="J58" s="2" t="n">
         <v>1423</v>
       </c>
-      <c r="K58" s="2" t="inlineStr">
+      <c r="K58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3685,7 +4155,15 @@
       <c r="J59" s="2" t="n">
         <v>177</v>
       </c>
-      <c r="K59" s="2" t="inlineStr">
+      <c r="K59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1023 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3738,7 +4216,15 @@
       <c r="J60" s="2" t="n">
         <v>1413</v>
       </c>
-      <c r="K60" s="2" t="inlineStr">
+      <c r="K60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3791,7 +4277,15 @@
       <c r="J61" s="2" t="n">
         <v>163</v>
       </c>
-      <c r="K61" s="2" t="inlineStr">
+      <c r="K61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1037 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3844,7 +4338,15 @@
       <c r="J62" s="2" t="n">
         <v>360</v>
       </c>
-      <c r="K62" s="2" t="inlineStr">
+      <c r="K62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Needs 840 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3897,7 +4399,15 @@
       <c r="J63" s="2" t="n">
         <v>484</v>
       </c>
-      <c r="K63" s="2" t="inlineStr">
+      <c r="K63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Needs 716 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -3950,7 +4460,15 @@
       <c r="J64" s="2" t="n">
         <v>386</v>
       </c>
-      <c r="K64" s="2" t="inlineStr">
+      <c r="K64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Needs 814 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4003,7 +4521,15 @@
       <c r="J65" s="2" t="n">
         <v>382</v>
       </c>
-      <c r="K65" s="2" t="inlineStr">
+      <c r="K65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Needs 818 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4056,7 +4582,15 @@
       <c r="J66" s="2" t="n">
         <v>97</v>
       </c>
-      <c r="K66" s="2" t="inlineStr">
+      <c r="K66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1103 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4109,7 +4643,15 @@
       <c r="J67" s="2" t="n">
         <v>369</v>
       </c>
-      <c r="K67" s="2" t="inlineStr">
+      <c r="K67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Needs 831 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4162,7 +4704,15 @@
       <c r="J68" s="2" t="n">
         <v>728</v>
       </c>
-      <c r="K68" s="2" t="inlineStr">
+      <c r="K68" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Needs 472 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4215,7 +4765,15 @@
       <c r="J69" s="2" t="n">
         <v>510</v>
       </c>
-      <c r="K69" s="2" t="inlineStr">
+      <c r="K69" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Needs 690 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4268,7 +4826,15 @@
       <c r="J70" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="K70" s="2" t="inlineStr">
+      <c r="K70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Needs 672 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4321,7 +4887,15 @@
       <c r="J71" s="2" t="n">
         <v>207</v>
       </c>
-      <c r="K71" s="2" t="inlineStr">
+      <c r="K71" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Needs 993 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4374,7 +4948,15 @@
       <c r="J72" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="K72" s="2" t="inlineStr">
+      <c r="K72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1110 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4427,7 +5009,15 @@
       <c r="J73" s="2" t="n">
         <v>141</v>
       </c>
-      <c r="K73" s="2" t="inlineStr">
+      <c r="K73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4480,7 +5070,15 @@
       <c r="J74" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="K74" s="2" t="inlineStr">
+      <c r="K74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1041 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4533,7 +5131,15 @@
       <c r="J75" s="2" t="n">
         <v>528</v>
       </c>
-      <c r="K75" s="2" t="inlineStr">
+      <c r="K75" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Needs 672 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4586,7 +5192,15 @@
       <c r="J76" s="2" t="n">
         <v>563</v>
       </c>
-      <c r="K76" s="2" t="inlineStr">
+      <c r="K76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Needs 637 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4639,7 +5253,15 @@
       <c r="J77" s="2" t="n">
         <v>483</v>
       </c>
-      <c r="K77" s="2" t="inlineStr">
+      <c r="K77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Needs 717 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4692,7 +5314,15 @@
       <c r="J78" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="K78" s="2" t="inlineStr">
+      <c r="K78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1108 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4745,7 +5375,15 @@
       <c r="J79" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="K79" s="2" t="inlineStr">
+      <c r="K79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1025 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4798,7 +5436,15 @@
       <c r="J80" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K80" s="2" t="inlineStr">
+      <c r="K80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1100 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4851,7 +5497,15 @@
       <c r="J81" s="2" t="n">
         <v>179</v>
       </c>
-      <c r="K81" s="2" t="inlineStr">
+      <c r="K81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1021 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4904,7 +5558,15 @@
       <c r="J82" s="2" t="n">
         <v>578</v>
       </c>
-      <c r="K82" s="2" t="inlineStr">
+      <c r="K82" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Needs 622 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -4957,7 +5619,15 @@
       <c r="J83" s="2" t="n">
         <v>1413</v>
       </c>
-      <c r="K83" s="2" t="inlineStr">
+      <c r="K83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5010,7 +5680,15 @@
       <c r="J84" s="2" t="n">
         <v>801</v>
       </c>
-      <c r="K84" s="2" t="inlineStr">
+      <c r="K84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Needs 399 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5063,7 +5741,15 @@
       <c r="J85" s="2" t="n">
         <v>379</v>
       </c>
-      <c r="K85" s="2" t="inlineStr">
+      <c r="K85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Needs 821 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5116,7 +5802,15 @@
       <c r="J86" s="2" t="n">
         <v>91</v>
       </c>
-      <c r="K86" s="2" t="inlineStr">
+      <c r="K86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1109 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5169,7 +5863,15 @@
       <c r="J87" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="K87" s="2" t="inlineStr">
+      <c r="K87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1098 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5222,7 +5924,15 @@
       <c r="J88" s="2" t="n">
         <v>813</v>
       </c>
-      <c r="K88" s="2" t="inlineStr">
+      <c r="K88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Needs 387 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5275,7 +5985,15 @@
       <c r="J89" s="2" t="n">
         <v>1414</v>
       </c>
-      <c r="K89" s="2" t="inlineStr">
+      <c r="K89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5328,7 +6046,15 @@
       <c r="J90" s="2" t="n">
         <v>542</v>
       </c>
-      <c r="K90" s="2" t="inlineStr">
+      <c r="K90" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Needs 658 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5381,7 +6107,15 @@
       <c r="J91" s="2" t="n">
         <v>93</v>
       </c>
-      <c r="K91" s="2" t="inlineStr">
+      <c r="K91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1107 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5434,7 +6168,15 @@
       <c r="J92" s="2" t="n">
         <v>461</v>
       </c>
-      <c r="K92" s="2" t="inlineStr">
+      <c r="K92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Needs 739 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5487,7 +6229,15 @@
       <c r="J93" s="2" t="n">
         <v>364</v>
       </c>
-      <c r="K93" s="2" t="inlineStr">
+      <c r="K93" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Needs 836 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5540,7 +6290,15 @@
       <c r="J94" s="2" t="n">
         <v>1416</v>
       </c>
-      <c r="K94" s="2" t="inlineStr">
+      <c r="K94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5593,7 +6351,15 @@
       <c r="J95" s="2" t="n">
         <v>1423</v>
       </c>
-      <c r="K95" s="2" t="inlineStr">
+      <c r="K95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5646,7 +6412,15 @@
       <c r="J96" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K96" s="2" t="inlineStr">
+      <c r="K96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1100 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5699,7 +6473,15 @@
       <c r="J97" s="2" t="n">
         <v>180</v>
       </c>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="K97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1020 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5752,7 +6534,15 @@
       <c r="J98" s="2" t="n">
         <v>218</v>
       </c>
-      <c r="K98" s="2" t="inlineStr">
+      <c r="K98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5805,7 +6595,15 @@
       <c r="J99" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="K99" s="2" t="inlineStr">
+      <c r="K99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5858,7 +6656,15 @@
       <c r="J100" s="2" t="n">
         <v>209</v>
       </c>
-      <c r="K100" s="2" t="inlineStr">
+      <c r="K100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5911,7 +6717,15 @@
       <c r="J101" s="2" t="n">
         <v>153</v>
       </c>
-      <c r="K101" s="2" t="inlineStr">
+      <c r="K101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -5964,7 +6778,15 @@
       <c r="J102" s="2" t="n">
         <v>146</v>
       </c>
-      <c r="K102" s="2" t="inlineStr">
+      <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6017,7 +6839,15 @@
       <c r="J103" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K103" s="2" t="inlineStr">
+      <c r="K103" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6070,7 +6900,15 @@
       <c r="J104" s="2" t="n">
         <v>1407</v>
       </c>
-      <c r="K104" s="2" t="inlineStr">
+      <c r="K104" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6123,7 +6961,15 @@
       <c r="J105" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="K105" s="2" t="inlineStr">
+      <c r="K105" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6176,7 +7022,15 @@
       <c r="J106" s="2" t="n">
         <v>168</v>
       </c>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="K106" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6229,7 +7083,15 @@
       <c r="J107" s="2" t="n">
         <v>195</v>
       </c>
-      <c r="K107" s="2" t="inlineStr">
+      <c r="K107" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6282,7 +7144,15 @@
       <c r="J108" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K108" s="2" t="inlineStr">
+      <c r="K108" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1100 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6335,7 +7205,15 @@
       <c r="J109" s="2" t="n">
         <v>158</v>
       </c>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="K109" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6388,7 +7266,15 @@
       <c r="J110" s="2" t="n">
         <v>463</v>
       </c>
-      <c r="K110" s="2" t="inlineStr">
+      <c r="K110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Needs 737 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6441,7 +7327,15 @@
       <c r="J111" s="2" t="n">
         <v>1433</v>
       </c>
-      <c r="K111" s="2" t="inlineStr">
+      <c r="K111" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6494,7 +7388,15 @@
       <c r="J112" s="2" t="n">
         <v>385</v>
       </c>
-      <c r="K112" s="2" t="inlineStr">
+      <c r="K112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Needs 815 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6547,7 +7449,15 @@
       <c r="J113" s="2" t="n">
         <v>546</v>
       </c>
-      <c r="K113" s="2" t="inlineStr">
+      <c r="K113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Needs 654 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6600,7 +7510,15 @@
       <c r="J114" s="2" t="n">
         <v>389</v>
       </c>
-      <c r="K114" s="2" t="inlineStr">
+      <c r="K114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Needs 811 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6653,7 +7571,15 @@
       <c r="J115" s="2" t="n">
         <v>1428</v>
       </c>
-      <c r="K115" s="2" t="inlineStr">
+      <c r="K115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6706,7 +7632,15 @@
       <c r="J116" s="2" t="n">
         <v>521</v>
       </c>
-      <c r="K116" s="2" t="inlineStr">
+      <c r="K116" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Needs 679 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M116" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6759,7 +7693,15 @@
       <c r="J117" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="K117" s="2" t="inlineStr">
+      <c r="K117" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1110 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M117" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6812,7 +7754,15 @@
       <c r="J118" s="2" t="n">
         <v>384</v>
       </c>
-      <c r="K118" s="2" t="inlineStr">
+      <c r="K118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Needs 816 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M118" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6865,7 +7815,15 @@
       <c r="J119" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="K119" s="2" t="inlineStr">
+      <c r="K119" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M119" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6918,7 +7876,15 @@
       <c r="J120" s="2" t="n">
         <v>161</v>
       </c>
-      <c r="K120" s="2" t="inlineStr">
+      <c r="K120" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L120" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1039 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M120" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -6971,7 +7937,15 @@
       <c r="J121" s="2" t="n">
         <v>164</v>
       </c>
-      <c r="K121" s="2" t="inlineStr">
+      <c r="K121" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1036 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M121" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7024,7 +7998,15 @@
       <c r="J122" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="K122" s="2" t="inlineStr">
+      <c r="K122" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L122" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1015 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M122" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7077,7 +8059,15 @@
       <c r="J123" s="2" t="n">
         <v>175</v>
       </c>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="K123" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L123" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1025 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M123" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7130,7 +8120,15 @@
       <c r="J124" s="2" t="n">
         <v>380</v>
       </c>
-      <c r="K124" s="2" t="inlineStr">
+      <c r="K124" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L124" s="2" t="inlineStr">
+        <is>
+          <t>Needs 820 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M124" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7183,7 +8181,15 @@
       <c r="J125" s="2" t="n">
         <v>479</v>
       </c>
-      <c r="K125" s="2" t="inlineStr">
+      <c r="K125" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L125" s="2" t="inlineStr">
+        <is>
+          <t>Needs 721 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M125" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7236,7 +8242,15 @@
       <c r="J126" s="2" t="n">
         <v>791</v>
       </c>
-      <c r="K126" s="2" t="inlineStr">
+      <c r="K126" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L126" s="2" t="inlineStr">
+        <is>
+          <t>Needs 409 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M126" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7289,7 +8303,15 @@
       <c r="J127" s="2" t="n">
         <v>1412</v>
       </c>
-      <c r="K127" s="2" t="inlineStr">
+      <c r="K127" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L127" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M127" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7342,7 +8364,15 @@
       <c r="J128" s="2" t="n">
         <v>507</v>
       </c>
-      <c r="K128" s="2" t="inlineStr">
+      <c r="K128" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L128" s="2" t="inlineStr">
+        <is>
+          <t>Needs 693 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M128" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7395,7 +8425,15 @@
       <c r="J129" s="2" t="n">
         <v>155</v>
       </c>
-      <c r="K129" s="2" t="inlineStr">
+      <c r="K129" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M129" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7448,7 +8486,15 @@
       <c r="J130" s="2" t="n">
         <v>150</v>
       </c>
-      <c r="K130" s="2" t="inlineStr">
+      <c r="K130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L130" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M130" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7501,7 +8547,15 @@
       <c r="J131" s="2" t="n">
         <v>137</v>
       </c>
-      <c r="K131" s="2" t="inlineStr">
+      <c r="K131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L131" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M131" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7554,7 +8608,15 @@
       <c r="J132" s="2" t="n">
         <v>159</v>
       </c>
-      <c r="K132" s="2" t="inlineStr">
+      <c r="K132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L132" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M132" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7607,7 +8669,15 @@
       <c r="J133" s="2" t="n">
         <v>142</v>
       </c>
-      <c r="K133" s="2" t="inlineStr">
+      <c r="K133" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L133" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M133" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7660,7 +8730,15 @@
       <c r="J134" s="2" t="n">
         <v>133</v>
       </c>
-      <c r="K134" s="2" t="inlineStr">
+      <c r="K134" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L134" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M134" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7713,7 +8791,15 @@
       <c r="J135" s="2" t="n">
         <v>206</v>
       </c>
-      <c r="K135" s="2" t="inlineStr">
+      <c r="K135" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M135" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7766,7 +8852,15 @@
       <c r="J136" s="2" t="n">
         <v>162</v>
       </c>
-      <c r="K136" s="2" t="inlineStr">
+      <c r="K136" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M136" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7819,7 +8913,15 @@
       <c r="J137" s="2" t="n">
         <v>174</v>
       </c>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="K137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M137" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7872,7 +8974,15 @@
       <c r="J138" s="2" t="n">
         <v>165</v>
       </c>
-      <c r="K138" s="2" t="inlineStr">
+      <c r="K138" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L138" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1035 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M138" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7925,7 +9035,15 @@
       <c r="J139" s="2" t="n">
         <v>172</v>
       </c>
-      <c r="K139" s="2" t="inlineStr">
+      <c r="K139" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1028 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -7978,7 +9096,15 @@
       <c r="J140" s="2" t="n">
         <v>92</v>
       </c>
-      <c r="K140" s="2" t="inlineStr">
+      <c r="K140" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1108 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8031,7 +9157,15 @@
       <c r="J141" s="2" t="n">
         <v>514</v>
       </c>
-      <c r="K141" s="2" t="inlineStr">
+      <c r="K141" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L141" s="2" t="inlineStr">
+        <is>
+          <t>Needs 686 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M141" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8084,7 +9218,15 @@
       <c r="J142" s="2" t="n">
         <v>95</v>
       </c>
-      <c r="K142" s="2" t="inlineStr">
+      <c r="K142" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L142" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1105 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M142" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8137,7 +9279,15 @@
       <c r="J143" s="2" t="n">
         <v>108</v>
       </c>
-      <c r="K143" s="2" t="inlineStr">
+      <c r="K143" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L143" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1092 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M143" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8190,7 +9340,15 @@
       <c r="J144" s="2" t="n">
         <v>774</v>
       </c>
-      <c r="K144" s="2" t="inlineStr">
+      <c r="K144" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L144" s="2" t="inlineStr">
+        <is>
+          <t>Needs 426 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M144" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8243,7 +9401,15 @@
       <c r="J145" s="2" t="n">
         <v>1425</v>
       </c>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="K145" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L145" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M145" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8296,7 +9462,15 @@
       <c r="J146" s="2" t="n">
         <v>413</v>
       </c>
-      <c r="K146" s="2" t="inlineStr">
+      <c r="K146" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L146" s="2" t="inlineStr">
+        <is>
+          <t>Needs 787 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M146" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8349,7 +9523,15 @@
       <c r="J147" s="2" t="n">
         <v>1423</v>
       </c>
-      <c r="K147" s="2" t="inlineStr">
+      <c r="K147" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L147" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M147" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8402,7 +9584,15 @@
       <c r="J148" s="2" t="n">
         <v>518</v>
       </c>
-      <c r="K148" s="2" t="inlineStr">
+      <c r="K148" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L148" s="2" t="inlineStr">
+        <is>
+          <t>Needs 682 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M148" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8455,7 +9645,15 @@
       <c r="J149" s="2" t="n">
         <v>192</v>
       </c>
-      <c r="K149" s="2" t="inlineStr">
+      <c r="K149" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L149" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1008 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M149" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8508,7 +9706,15 @@
       <c r="J150" s="2" t="n">
         <v>207</v>
       </c>
-      <c r="K150" s="2" t="inlineStr">
+      <c r="K150" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>Needs 993 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M150" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8561,7 +9767,15 @@
       <c r="J151" s="2" t="n">
         <v>1412</v>
       </c>
-      <c r="K151" s="2" t="inlineStr">
+      <c r="K151" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L151" s="2" t="inlineStr">
+        <is>
+          <t>Needs 0 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M151" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8614,7 +9828,15 @@
       <c r="J152" s="2" t="n">
         <v>308</v>
       </c>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="K152" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L152" s="2" t="inlineStr">
+        <is>
+          <t>Needs 892 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M152" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8667,7 +9889,15 @@
       <c r="J153" s="2" t="n">
         <v>457</v>
       </c>
-      <c r="K153" s="2" t="inlineStr">
+      <c r="K153" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L153" s="2" t="inlineStr">
+        <is>
+          <t>Needs 743 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M153" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8720,7 +9950,15 @@
       <c r="J154" s="2" t="n">
         <v>102</v>
       </c>
-      <c r="K154" s="2" t="inlineStr">
+      <c r="K154" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L154" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1098 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M154" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8773,7 +10011,15 @@
       <c r="J155" s="2" t="n">
         <v>205</v>
       </c>
-      <c r="K155" s="2" t="inlineStr">
+      <c r="K155" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L155" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M155" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8826,7 +10072,15 @@
       <c r="J156" s="2" t="n">
         <v>171</v>
       </c>
-      <c r="K156" s="2" t="inlineStr">
+      <c r="K156" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L156" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M156" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8879,7 +10133,15 @@
       <c r="J157" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="K157" s="2" t="inlineStr">
+      <c r="K157" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L157" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M157" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8932,7 +10194,15 @@
       <c r="J158" s="2" t="n">
         <v>393</v>
       </c>
-      <c r="K158" s="2" t="inlineStr">
+      <c r="K158" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>Needs 807 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -8985,7 +10255,15 @@
       <c r="J159" s="2" t="n">
         <v>350</v>
       </c>
-      <c r="K159" s="2" t="inlineStr">
+      <c r="K159" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>Needs 850 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9038,7 +10316,15 @@
       <c r="J160" s="2" t="n">
         <v>184</v>
       </c>
-      <c r="K160" s="2" t="inlineStr">
+      <c r="K160" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L160" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M160" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9091,7 +10377,15 @@
       <c r="J161" s="2" t="n">
         <v>181</v>
       </c>
-      <c r="K161" s="2" t="inlineStr">
+      <c r="K161" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L161" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M161" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9144,7 +10438,15 @@
       <c r="J162" s="2" t="n">
         <v>90</v>
       </c>
-      <c r="K162" s="2" t="inlineStr">
+      <c r="K162" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L162" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1110 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M162" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9197,7 +10499,15 @@
       <c r="J163" s="2" t="n">
         <v>797</v>
       </c>
-      <c r="K163" s="2" t="inlineStr">
+      <c r="K163" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L163" s="2" t="inlineStr">
+        <is>
+          <t>Needs 403 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M163" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9250,7 +10560,15 @@
       <c r="J164" s="2" t="n">
         <v>185</v>
       </c>
-      <c r="K164" s="2" t="inlineStr">
+      <c r="K164" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L164" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1015 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M164" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9303,7 +10621,15 @@
       <c r="J165" s="2" t="n">
         <v>795</v>
       </c>
-      <c r="K165" s="2" t="inlineStr">
+      <c r="K165" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L165" s="2" t="inlineStr">
+        <is>
+          <t>Needs 405 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M165" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9356,7 +10682,15 @@
       <c r="J166" s="2" t="n">
         <v>366</v>
       </c>
-      <c r="K166" s="2" t="inlineStr">
+      <c r="K166" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L166" s="2" t="inlineStr">
+        <is>
+          <t>Needs 834 words; 8 sources</t>
+        </is>
+      </c>
+      <c r="M166" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9409,7 +10743,15 @@
       <c r="J167" s="2" t="n">
         <v>149</v>
       </c>
-      <c r="K167" s="2" t="inlineStr">
+      <c r="K167" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L167" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M167" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9462,7 +10804,15 @@
       <c r="J168" s="2" t="n">
         <v>213</v>
       </c>
-      <c r="K168" s="2" t="inlineStr">
+      <c r="K168" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M168" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9515,7 +10865,15 @@
       <c r="J169" s="2" t="n">
         <v>156</v>
       </c>
-      <c r="K169" s="2" t="inlineStr">
+      <c r="K169" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9568,7 +10926,15 @@
       <c r="J170" s="2" t="n">
         <v>128</v>
       </c>
-      <c r="K170" s="2" t="inlineStr">
+      <c r="K170" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9621,7 +10987,15 @@
       <c r="J171" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K171" s="2" t="inlineStr">
+      <c r="K171" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9674,7 +11048,15 @@
       <c r="J172" s="2" t="n">
         <v>166</v>
       </c>
-      <c r="K172" s="2" t="inlineStr">
+      <c r="K172" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9727,7 +11109,15 @@
       <c r="J173" s="2" t="n">
         <v>140</v>
       </c>
-      <c r="K173" s="2" t="inlineStr">
+      <c r="K173" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9780,7 +11170,15 @@
       <c r="J174" s="2" t="n">
         <v>158</v>
       </c>
-      <c r="K174" s="2" t="inlineStr">
+      <c r="K174" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9833,7 +11231,15 @@
       <c r="J175" s="2" t="n">
         <v>178</v>
       </c>
-      <c r="K175" s="2" t="inlineStr">
+      <c r="K175" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9886,7 +11292,15 @@
       <c r="J176" s="2" t="n">
         <v>170</v>
       </c>
-      <c r="K176" s="2" t="inlineStr">
+      <c r="K176" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>Not in long-form scope</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9939,7 +11353,15 @@
       <c r="J177" s="2" t="n">
         <v>100</v>
       </c>
-      <c r="K177" s="2" t="inlineStr">
+      <c r="K177" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>Needs 1100 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
@@ -9992,19 +11414,6490 @@
       <c r="J178" s="2" t="n">
         <v>216</v>
       </c>
-      <c r="K178" s="2" t="inlineStr">
+      <c r="K178" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>Needs 984 words; 9 sources</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
         <is>
           <t>Supporting page</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K178"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L119"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="54" customWidth="1" min="5" max="5"/>
+    <col width="58" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="76" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Cluster</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Slug</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Title (EN)</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Canonical EN</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>English words</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>Source count</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Required words</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>Required sources</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>Next action</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-assessment-is-multidisciplinary</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: bariatric assessment is broader than a weight number</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/bariatric-assessment-is-multidisciplinary</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-follow-up-is-lifelong</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: follow-up after bariatric surgery is lifelong</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/bariatric-follow-up-is-lifelong</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-vitamin-monitoring</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Vitamin monitoring after bariatric surgery: why not rely on a random supplement?</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/bariatric-vitamin-monitoring</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>preparing-for-bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Before bariatric surgery: assessment, preparation and questions to ask</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/preparing-for-bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>516</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>sleeve-gastrectomy-nutrition-follow-up</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Nutrition and follow-up after sleeve gastrectomy: why is the plan individual?</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/sleeve-gastrectomy-nutrition-follow-up</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>sleeve-gastrectomy-operation-day-recovery</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Sleeve gastrectomy day and early recovery: preparation and follow-up questions</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/sleeve-gastrectomy-operation-day-recovery</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1426</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>bariatric-surgery</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>sleeve-gastrectomy-what-to-know</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Sleeve gastrectomy: how is it done, and what should you know before deciding?</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/sleeve-gastrectomy-what-to-know</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>228</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring-safety-first</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: non-surgical body contouring is a medical procedure, not a risk-free session</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/body-contouring-safety-first</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>383</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring-vs-weight-loss</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>The difference between body contouring and weight loss</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/body-contouring-vs-weight-loss</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>580</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>body-fat-percentage-context-men-women</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Body-fat percentage for men and women: why one number is not enough</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/body-fat-percentage-context-men-women</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1440</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>cellulite-exercise-realistic-expectations</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Cellulite and exercise: what may improve and what exercise cannot promise</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/cellulite-exercise-realistic-expectations</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1424</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>cellulite-home-care-and-safety</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Cellulite at home: realistic care and when assessment is needed</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/cellulite-home-care-and-safety</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>cellulite-is-a-skin-structure-feature</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: cellulite reflects skin structure, not a measure of obesity</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/cellulite-is-a-skin-structure-feature</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>cellulite-realistic-options-and-limits</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Cellulite: why it appears, and the limits of exercise, creams and contouring procedures</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/cellulite-realistic-options-and-limits</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>fat-dissolving-injections-side-effects-safety</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Fat-dissolving injections: ingredients, side effects and safety questions</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/fat-dissolving-injections-side-effects-safety</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>inbody-test-first-visit-guide</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Your first InBody test: what it measures and how to prepare</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/inbody-test-first-visit-guide</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>local-fat-injections-do-they-work</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>What are local fat-dissolving injections, and do they really work?</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/local-fat-injections-do-they-work</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>600</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>loose-skin-or-localised-fat</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Loose skin or localised fat after weight loss? The difference changes the choice</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/loose-skin-or-localised-fat</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>473</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>mesotherapy-needs-an-ingredient-level-check</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: with mesotherapy, the injected substance and site must be clear</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/mesotherapy-needs-an-ingredient-level-check</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>176</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>body-contouring</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>stubborn-localised-fat</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Stubborn localised fat: why diet alone may not change one area</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/stubborn-localised-fat</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>body-composition-change-over-time</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Following body composition: how to compare measurements fairly</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/body-composition-change-over-time</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>body-composition-not-scale</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Body composition is not the scale: why InBody matters in follow-up</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/body-composition-not-scale</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>788</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>inbody-preparation-for-reliable-follow-up</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Preparing for an InBody analysis: how to make follow-up comparisons fairer</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/inbody-preparation-for-reliable-follow-up</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>214</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>inbody-results-explained</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>InBody analysis: what it measures and how to read the result</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/inbody-results-explained</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>607</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>insulin-resistance-explained</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Insulin resistance: what it means and why weight can feel stuck</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/insulin-resistance-explained</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>muscle-assessment-in-nutrition-care</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: muscle assessment belongs in nutrition care</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/muscle-assessment-in-nutrition-care</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>381</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>pcos-and-weight</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>PCOS and weight: understanding the hormonal loop and what helps</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/pcos-and-weight</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>794</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>protecting-muscle-while-losing-weight</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>How to protect muscle while losing weight</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/protecting-muscle-while-losing-weight</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>supplements-are-targeted-not-a-default</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: supplements should answer a clear need, not become a default</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/supplements-are-targeted-not-a-default</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>209</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>therapeutic-nutrition-first-visit-guide</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Your first therapeutic-nutrition visit: preparing for a sustainable plan</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/therapeutic-nutrition-first-visit-guide</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>1433</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>clinical-nutrition</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>vitamin-b12-in-plant-based-eating</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: plant-based eating needs a planned source of vitamin B12</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/vitamin-b12-in-plant-based-eating</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>188</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>acne-care-is-gentle-not-aggressive</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: acne does not mean skin needs harsher scrubbing</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-care-is-gentle-not-aggressive</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>154</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>acne-in-pregnancy-safe-assessment</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Acne in pregnancy: why does the skincare routine need review?</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-in-pregnancy-safe-assessment</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>acne-in-teen-girls-assessment</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Acne in teenage girls: when to review the routine and seek assessment</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-in-teen-girls-assessment</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>acne-marks-and-scars-what-is-the-difference</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Acne marks and scars: what is the difference, and when do they need treatment?</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-marks-and-scars-what-is-the-difference</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>acne-oily-skin-gentle-routine</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Acne and oily skin: a gentle routine and useful questions for dermatology</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-oily-skin-gentle-routine</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>acne-safe-home-care-and-when-to-check</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Acne at home: a gentle routine and when you need a treatment plan</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acne-safe-home-care-and-when-to-check</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>163</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>biotin-before-blood-tests</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: biotin supplements can alter some blood-test results</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/biotin-before-blood-tests</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>dark-neck-acanthosis-insulin-resistance</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Dark skin on the neck and insulin resistance: when is the link relevant?</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/dark-neck-acanthosis-insulin-resistance</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>484</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>dark-neck-skin-during-pregnancy</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Dark neck skin during pregnancy: what is worth discussing with a doctor?</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/dark-neck-skin-during-pregnancy</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>386</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>deep-painful-acne-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Large, painful spots under the skin: why squeezing is not the answer</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/deep-painful-acne-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>382</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>eczema-flare-when-to-check</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Eczema flares: when to review the routine and when to see dermatology</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/eczema-flare-when-to-check</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>folliculitis-vs-acne-itchy-bumps</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Itchy bumps that look like acne: when might folliculitis be considered?</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/folliculitis-vs-acne-itchy-bumps</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>369</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>hair-loss-blood-tests-first</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Hair loss: why blood tests may come before any product</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hair-loss-blood-tests-first</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>728</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>hair-loss-in-men-when-to-get-checked</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Hair loss in men: what is common and what needs a check</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hair-loss-in-men-when-to-get-checked</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>510</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>hair-loss-in-women-causes-that-matter</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Hair loss in women: the causes that make a difference</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hair-loss-in-women-causes-that-matter</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>hormonal-acne-clues-and-assessment</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Hormonal acne: when is the label useful, and when do you need a broader assessment?</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hormonal-acne-clues-and-assessment</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>melasma-and-sun-protection</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Melasma and pigmentation: how to discuss protection and a realistic plan</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/melasma-and-sun-protection</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>dermatology</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>telogen-effluvium-sudden-hair-shedding</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Sudden shedding after illness or stress: when might telogen effluvium be considered?</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/telogen-effluvium-sudden-hair-shedding</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>159</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>abdominal-pelvic-ultrasound-what-it-shows</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Abdominal and pelvic ultrasound: what does it actually show?</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/abdominal-pelvic-ultrasound-what-it-shows</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>528</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>abdominal-ultrasound-what-it-shows</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>What can an abdominal ultrasound show:and what can it not show?</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/abdominal-ultrasound-what-it-shows</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>563</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>acid-reflux-when-to-see-doctor</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Acid reflux and heartburn: when can habits help and when should you seek care?</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/acid-reflux-when-to-see-doctor</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>bloating-when-to-see-doctor</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Bloating: when to follow the pattern and when to arrange assessment</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/bloating-when-to-see-doctor</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>coeliac-testing-before-gluten-free-diet</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: do not stop gluten before coeliac testing is complete</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/coeliac-testing-before-gluten-free-diet</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>colonoscopy-preparation-what-to-ask</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Preparing for colonoscopy: questions that help you follow the plan safely</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/colonoscopy-preparation-what-to-ask</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>fatty-liver-fibrosis-needs-its-own-assessment</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: liver fat and liver fibrosis are not the same measurement</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/fatty-liver-fibrosis-needs-its-own-assessment</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>179</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>fatty-liver-symptoms-diagnosis-risk</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Fatty liver: symptoms, diagnosis and when it becomes serious</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/fatty-liver-symptoms-diagnosis-risk</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>578</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>fatty-liver-treatment-and-follow-up</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Fatty liver: what belongs in a realistic treatment and follow-up plan?</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/fatty-liver-treatment-and-follow-up</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>fatty-liver-ultrasound</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Fatty liver: what this common abdominal-ultrasound finding means</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/fatty-liver-ultrasound</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>gastroscopy-vs-colonoscopy-what-to-expect</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Gastroscopy or colonoscopy: what is the difference, and when is each considered?</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gastroscopy-vs-colonoscopy-what-to-expect</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>379</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>gerd-and-reflux-difference</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Reflux and heartburn: when does a repeated symptom need assessment?</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gerd-and-reflux-difference</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-after-treatment-follow-up</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>After H. pylori treatment: why follow-up does not rely on symptoms alone</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-after-treatment-follow-up</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-reflux-ibs</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>H. pylori, reflux or IBS? How clinicians tell them apart</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-reflux-ibs</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-symptoms-and-testing-pathway</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>H. pylori: symptoms alone are not enough: how testing is considered</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-symptoms-and-testing-pathway</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>1414</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-symptoms-tests-treatment</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>H. pylori: symptoms, tests and when treatment is needed</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-symptoms-tests-treatment</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>542</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>heartburn-in-pregnancy-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Heartburn in pregnancy: when to discuss it with your care team</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/heartburn-in-pregnancy-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>ibs-colon-symptoms-red-flags</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>IBS symptoms: what fits the pattern and what needs investigation?</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/ibs-colon-symptoms-red-flags</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>461</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>ibs-symptoms-in-pregnancy-when-to-check</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>IBS-like symptoms in pregnancy: what should not be explained without assessment?</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/ibs-symptoms-in-pregnancy-when-to-check</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>364</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>ibs-symptoms-men-assessment-guide</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>IBS symptoms in men: when to track a pattern and when to seek assessment</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/ibs-symptoms-men-assessment-guide</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>1416</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>ibs-symptoms-women-assessment-guide</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>IBS symptoms in women: how to prepare for an organised assessment</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/ibs-symptoms-women-assessment-guide</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>liver-function-tests-need-context</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Liver function tests: why one number should not be interpreted alone</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/liver-function-tests-need-context</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>normal-ultrasound-does-not-end-assessment</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: a normal ultrasound does not always end an abdominal-pain assessment</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/normal-ultrasound-does-not-end-assessment</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>180</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>gastroenterology-hepatology</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>severe-ibs-symptoms-red-flags</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Severe IBS-like symptoms: which signs should not wait for assessment?</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/severe-ibs-symptoms-red-flags</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>general</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>food-intolerance-vs-allergy</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Food allergy and intolerance: why the difference needs assessment</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/food-intolerance-vs-allergy</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>abdominal-hernia-warning-signs</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Abdominal or groin hernia: when is it straightforward and when is it urgent?</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/abdominal-hernia-warning-signs</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>463</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>abdominal-wall-hernia-symptoms-guide</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Abdominal-wall hernia symptoms: bulge, pain and when to seek review</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/abdominal-wall-hernia-symptoms-guide</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>1433</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>after-gallbladder-surgery-recovery-warning-signs</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>After gallbladder surgery: what is expected in recovery, and what needs prompt contact?</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/after-gallbladder-surgery-recovery-warning-signs</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>385</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>gallbladder-laparoscopic-or-open-surgery</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Gallbladder surgery: laparoscopic or open, and what decides?</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gallbladder-laparoscopic-or-open-surgery</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>546</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>gallbladder-pain-in-pregnancy-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Gallbladder pain in pregnancy: why diagnosis needs coordinated assessment</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gallbladder-pain-in-pregnancy-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>389</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>gallbladder-surgery-operation-day-guide</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Gallbladder surgery day: how to prepare and what to ask</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gallbladder-surgery-operation-day-guide</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>1428</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>gallstones-symptoms-and-surgery</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Gallstones: when do they explain pain and when is surgery considered?</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gallstones-symptoms-and-surgery</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>521</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>gallstones-when-symptoms-need-assessment</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Gallstones: when does a symptom need assessment rather than guessing?</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/gallstones-when-symptoms-need-assessment</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>hernia-after-pregnancy-or-c-section</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>A bulge after pregnancy or a caesarean birth: when might a hernia be considered?</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hernia-after-pregnancy-or-c-section</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>384</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>silent-gallstones-usually-need-no-treatment</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: silent gallstones usually do not need treatment</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/silent-gallstones-usually-need-no-treatment</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>161</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>general-surgery</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>surgical-checks-are-a-team-pause</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: repeated safety questions before surgery are deliberate</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/surgical-checks-are-a-team-pause</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>164</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>blood-pressure-needs-a-pattern</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: diagnosing high blood pressure needs a pattern, not one number</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/blood-pressure-needs-a-pattern</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>diabetes-remission-is-not-cure</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: diabetes remission is not the same as a cure</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/diabetes-remission-is-not-cure</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>175</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>diabetes-review-whole-health</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: a diabetes review covers whole health, not HbA1c alone</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/diabetes-review-whole-health</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>380</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>high-cholesterol-results-and-next-steps</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>High cholesterol: understanding the test and deciding whether food changes are enough</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/high-cholesterol-results-and-next-steps</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>479</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>hypothyroidism-and-weight</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Hypothyroidism and weight gain: what is the real connection?</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hypothyroidism-and-weight</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>791</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>insulin-resistance-adults-symptoms-testing</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Insulin resistance: symptoms, tests and an organised assessment</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/insulin-resistance-adults-symptoms-testing</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>1412</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>kidney-stones-symptoms-and-tests</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Kidney stones: warning symptoms, ultrasound and useful tests</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/kidney-stones-symptoms-and-tests</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>507</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>internal-medicine</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>ultrasound-uses-sound-not-xrays</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: ultrasound uses sound waves, not X-rays</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/ultrasound-uses-sound-not-xrays</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>165</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>child-growth-is-a-trajectory</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: a child’s growth is a trajectory, not a single comparison</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/child-growth-is-a-trajectory</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>172</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>child-nutrition-growth-visit</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>A child nutrition and growth visit: what makes it useful?</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/child-nutrition-growth-visit</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>child-short-height-growth-curve</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Is my child short? Understanding the growth curve and when to assess it</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/child-short-height-growth-curve</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>514</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>child-vomiting-and-dehydration-warning-signs</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>A child’s vomiting and dehydration: details that help assessment</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/child-vomiting-and-dehydration-warning-signs</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>childhood-constipation-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Childhood constipation: when to adjust the routine and when to arrange assessment</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/childhood-constipation-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>108</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>childrens-appetite</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Children's appetite: when it is behavioural and when to look for a medical cause</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/childrens-appetite</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>774</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>dark-neck-skin-children-assessment</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Dark neck skin in children: when to review the skin and seek assessment</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/dark-neck-skin-children-assessment</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>endoscopy-in-children-when-considered</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Endoscopy in children: when might it be considered, and what happens before the decision?</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/endoscopy-in-children-when-considered</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>413</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-children-when-testing-considered</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>H. pylori in children: when might a clinician consider testing?</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-children-when-testing-considered</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J103" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>h-pylori-in-children-symptoms-tests</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>H. pylori in children: symptoms, tests and when to worry</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/h-pylori-in-children-symptoms-tests</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>518</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J104" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>hair-loss-in-children-when-to-check</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Hair loss in children: when can it be temporary, and when does it need a check?</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hair-loss-in-children-when-to-check</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>192</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J105" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>hernia-in-children-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Hernia in children: when does a bulge need assessment, and when is it urgent?</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/hernia-in-children-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>207</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J106" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>insulin-resistance-children-family-assessment</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>Insulin resistance in children: assessment and a family-centred plan</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/insulin-resistance-children-family-assessment</t>
+        </is>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>1412</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J107" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L107" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>insulin-resistance-in-children</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>Insulin resistance in children: what makes assessment useful, and what does not prove a diagnosis?</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/insulin-resistance-in-children</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>308</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L108" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>iron-deficiency-in-children</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>Iron deficiency in children: appetite, concentration, tests and treatment</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/iron-deficiency-in-children</t>
+        </is>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>457</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J109" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L109" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>iron-rich-foods-for-children</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>Iron-rich food for children: how to discuss choices without guessing</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/iron-rich-foods-for-children</t>
+        </is>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>102</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J110" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L110" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>recurrent-tummy-aches-in-children</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>Recurring tummy aches in children: when might a functional pattern fit, and when should another cause be checked?</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/recurrent-tummy-aches-in-children</t>
+        </is>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>393</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J111" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L111" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>responsive-complementary-feeding</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: complementary feeding should respond to the child, not force the plate</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/responsive-complementary-feeding</t>
+        </is>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>350</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J112" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L112" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>pediatrics</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>vitamin-d-in-children-when-to-assess</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>Vitamin D in children: when to review food, sun exposure and tests</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/vitamin-d-in-children-when-to-assess</t>
+        </is>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J113" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L113" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>glp1-medication-guide</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>GLP-1 medicines: a practical guide</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/glp1-medication-guide</t>
+        </is>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>797</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J114" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
+        <is>
+          <t>movement-benefits-beyond-the-scale</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: movement has health benefits even when the scale barely changes</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/movement-benefits-beyond-the-scale</t>
+        </is>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>185</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J115" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
+        <is>
+          <t>non-surgical-weight-options</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>Non-surgical alternatives to bariatric surgery: an honest comparison</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/non-surgical-weight-options</t>
+        </is>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J116" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L116" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
+        <is>
+          <t>obesity-care-beyond-bmi</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: obesity care goes beyond BMI</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/obesity-care-beyond-bmi</t>
+        </is>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>366</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J117" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L117" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>article</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
+        <is>
+          <t>weight-management-first-visit</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>A first weight-management visit: what goes into assessment beyond the scale?</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/weight-management-first-visit</t>
+        </is>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J118" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L118" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>Rewrite queue</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>update</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>weight-management</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
+        <is>
+          <t>weight-medicines-are-not-a-short-course</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>Scientific update: appetite-regulating weight medicines are not one short course for everyone</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>https://laroseclinics.com/en/articles/weight-medicines-are-not-a-short-course</t>
+        </is>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>216</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>1200</v>
+      </c>
+      <c r="J119" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L119" s="2" t="inlineStr">
+        <is>
+          <t>Keep canonical URL; run SERP review, write original update, add numbered citations and contextual internal links.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L119"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62255,7 +70148,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -62657,7 +70550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -65503,7 +73396,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
